--- a/33張resize結果_yolo26.xlsx
+++ b/33張resize結果_yolo26.xlsx
@@ -503,7 +503,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.779</v>
+        <v>0.768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -517,12 +517,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>176,51,269,288</t>
+          <t>173,40,272,294</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>❌否，請人工複查</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="J2" t="n">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.700422</v>
+        <v>2.519685</v>
       </c>
       <c r="M2" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0.771</v>
+        <v>0.724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53,137,180,397</t>
+          <t>54,127,183,400</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J3" t="n">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.461538</v>
+        <v>2.344322</v>
       </c>
       <c r="M3" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.764</v>
+        <v>0.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>112,64,247,388</t>
+          <t>128,61,242,386</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="J4" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.975309</v>
+        <v>1.969231</v>
       </c>
       <c r="M4" t="n">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -692,7 +692,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.745</v>
+        <v>0.841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>210,126,300,365</t>
+          <t>208,130,293,368</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J5" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.677824</v>
+        <v>2.689076</v>
       </c>
       <c r="M5" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -755,7 +755,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.745</v>
+        <v>0.862</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>113,99,242,380</t>
+          <t>124,104,236,374</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -783,10 +783,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="J6" t="n">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.27758</v>
+        <v>2.37037</v>
       </c>
       <c r="M6" t="n">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>0.767</v>
+        <v>0.844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>137,57,271,381</t>
+          <t>146,56,272,361</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="J7" t="n">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.975309</v>
+        <v>2.098361</v>
       </c>
       <c r="M7" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.752</v>
+        <v>0.825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>102,64,229,370</t>
+          <t>112,40,221,377</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="J8" t="n">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.091503</v>
+        <v>1.89911</v>
       </c>
       <c r="M8" t="n">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0.726</v>
+        <v>0.796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>142,92,237,343</t>
+          <t>146,94,233,341</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J9" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.549801</v>
+        <v>2.591093</v>
       </c>
       <c r="M9" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>0.696</v>
+        <v>0.76</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>162,126,281,394</t>
+          <t>168,123,275,385</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>❌否，請人工複查</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="J10" t="n">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.38806</v>
+        <v>2.442748</v>
       </c>
       <c r="M10" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>0.746</v>
+        <v>0.84</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>102,78,175,273</t>
+          <t>96,80,174,274</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.282051</v>
+        <v>3.298969</v>
       </c>
       <c r="M11" t="n">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>0.882</v>
+        <v>0.889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>130,85,249,386</t>
+          <t>128,75,251,385</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>❌否，請人工複查</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="J12" t="n">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.126246</v>
+        <v>2.064516</v>
       </c>
       <c r="M12" t="n">
         <v>193</v>
@@ -1196,7 +1196,7 @@
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>212,99,322,357</t>
+          <t>213,91,326,362</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>❌否，請人工複查</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="J13" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.48062</v>
+        <v>2.361624</v>
       </c>
       <c r="M13" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1259,7 +1259,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>0.759</v>
+        <v>0.847</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>106,87,231,375</t>
+          <t>116,77,225,372</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="J14" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.222222</v>
+        <v>2.169492</v>
       </c>
       <c r="M14" t="n">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>0.642</v>
+        <v>0.704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>137,3,240,261</t>
+          <t>143,0,238,254</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J15" t="n">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.48062</v>
+        <v>2.519685</v>
       </c>
       <c r="M15" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>0.711</v>
+        <v>0.782</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>156,35,249,297</t>
+          <t>160,34,242,304</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J16" t="n">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.442748</v>
+        <v>2.37037</v>
       </c>
       <c r="M16" t="n">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>0.774</v>
+        <v>0.804</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>179,71,263,305</t>
+          <t>179,70,260,308</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J17" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.735043</v>
+        <v>2.689076</v>
       </c>
       <c r="M17" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.784</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69,69,209,385</t>
+          <t>82,73,206,386</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="J18" t="n">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.025316</v>
+        <v>2.044728</v>
       </c>
       <c r="M18" t="n">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.695</v>
+        <v>0.801</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>140,92,264,394</t>
+          <t>152,100,261,398</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="J19" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.119205</v>
+        <v>2.147651</v>
       </c>
       <c r="M19" t="n">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>0.717</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>181,89,311,394</t>
+          <t>192,70,309,394</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>❌否，請人工複查</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="J20" t="n">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.098361</v>
+        <v>1.975309</v>
       </c>
       <c r="M20" t="n">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>0.769</v>
+        <v>0.785</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>98,148,207,371</t>
+          <t>96,149,204,374</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J21" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.869955</v>
+        <v>2.844444</v>
       </c>
       <c r="M21" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>0.783</v>
+        <v>0.902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>146,136,262,400</t>
+          <t>155,129,254,398</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="J22" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.424242</v>
+        <v>2.379182</v>
       </c>
       <c r="M22" t="n">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>0.742</v>
+        <v>0.858</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>88,96,217,399</t>
+          <t>101,95,212,400</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="J23" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.112211</v>
+        <v>2.098361</v>
       </c>
       <c r="M23" t="n">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>0.77</v>
+        <v>0.899</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>110,141,252,390</t>
+          <t>121,133,241,387</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="J24" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.570281</v>
+        <v>2.519685</v>
       </c>
       <c r="M24" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0.748</v>
+        <v>0.796</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>215,126,334,369</t>
+          <t>218,120,330,368</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J25" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.633745</v>
+        <v>2.580645</v>
       </c>
       <c r="M25" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2015,7 +2015,7 @@
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>0.747</v>
+        <v>0.889</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>92,77,199,346</t>
+          <t>83,78,190,344</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2046,7 +2046,7 @@
         <v>107</v>
       </c>
       <c r="J26" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.379182</v>
+        <v>2.406015</v>
       </c>
       <c r="M26" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>0.772</v>
+        <v>0.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>152,75,289,361</t>
+          <t>162,69,291,354</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="J27" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.237762</v>
+        <v>2.245614</v>
       </c>
       <c r="M27" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>0.717</v>
+        <v>0.838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>92,113,218,377</t>
+          <t>99,108,208,377</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="J28" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.424242</v>
+        <v>2.379182</v>
       </c>
       <c r="M28" t="n">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>0.734</v>
+        <v>0.83</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>172,117,304,400</t>
+          <t>185,105,302,400</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="J29" t="n">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.261484</v>
+        <v>2.169492</v>
       </c>
       <c r="M29" t="n">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>0.836</v>
+        <v>0.828</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>112,144,211,364</t>
+          <t>113,133,212,365</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2298,7 +2298,7 @@
         <v>99</v>
       </c>
       <c r="J30" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.909091</v>
+        <v>2.758621</v>
       </c>
       <c r="M30" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>0.918</v>
+        <v>0.928</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>143,73,261,370</t>
+          <t>146,61,263,363</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J31" t="n">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.154882</v>
+        <v>2.119205</v>
       </c>
       <c r="M31" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2393,7 +2393,7 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>0.713</v>
+        <v>0.827</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>167,104,303,400</t>
+          <t>180,107,299,400</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="J32" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.162162</v>
+        <v>2.1843</v>
       </c>
       <c r="M32" t="n">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>0.759</v>
+        <v>0.784</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>74,123,204,400</t>
+          <t>84,109,204,400</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J33" t="n">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.310469</v>
+        <v>2.199313</v>
       </c>
       <c r="M33" t="n">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>0.786</v>
+        <v>0.779</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2533,12 +2533,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>130,96,261,373</t>
+          <t>141,92,251,365</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>❌否，請人工複查</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="J34" t="n">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.310469</v>
+        <v>2.344322</v>
       </c>
       <c r="M34" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
